--- a/artfynd/A 30534-2025 artfynd.xlsx
+++ b/artfynd/A 30534-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ9"/>
+  <dimension ref="A1:AZ21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1156,10 +1156,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>135484978</v>
+        <v>136636551</v>
       </c>
       <c r="B6" t="n">
-        <v>92065</v>
+        <v>92373</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1167,37 +1167,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Spelåsens östsluttning, Ång</t>
+          <t>Öst om spelåsen, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>644921</v>
+        <v>644777</v>
       </c>
       <c r="R6" t="n">
-        <v>6973470</v>
+        <v>6973539</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1221,12 +1221,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1237,45 +1247,28 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>stormrensad lucka i naturskogsartad gammal granskog i långsträckt, fuktig bergssvacka</t>
-        </is>
-      </c>
-      <c r="AN6" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>1 substratenheter # 50 cm bred förrötad granlåga</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135484978</t>
+          <t>https://artportalen.se/Sighting/136636551</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>135484981</v>
+        <v>135484978</v>
       </c>
       <c r="B7" t="n">
         <v>92065</v>
@@ -1310,10 +1303,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>644762</v>
+        <v>644921</v>
       </c>
       <c r="R7" t="n">
-        <v>6973566</v>
+        <v>6973470</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1359,7 +1352,7 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>gammal olikåldrig grannaturskog i långsträckt, fuktig bergssvacka</t>
+          <t>stormrensad lucka i naturskogsartad gammal granskog i långsträckt, fuktig bergssvacka</t>
         </is>
       </c>
       <c r="AN7" t="n">
@@ -1367,7 +1360,7 @@
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>1 substratenheter # 20 cm bred förrötad granlåga</t>
+          <t>1 substratenheter # 50 cm bred förrötad granlåga</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1388,38 +1381,38 @@
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135484981</t>
+          <t>https://artportalen.se/Sighting/135484978</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>135484974</v>
+        <v>135484981</v>
       </c>
       <c r="B8" t="n">
-        <v>92079</v>
+        <v>92065</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1429,10 +1422,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>644999</v>
+        <v>644762</v>
       </c>
       <c r="R8" t="n">
-        <v>6973387</v>
+        <v>6973566</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1478,7 +1471,7 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>140-årig grannaturskog i blockig östsluttning</t>
+          <t>gammal olikåldrig grannaturskog i långsträckt, fuktig bergssvacka</t>
         </is>
       </c>
       <c r="AN8" t="n">
@@ -1486,7 +1479,7 @@
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>1 substratenheter # gammal murken granlåga</t>
+          <t>1 substratenheter # 20 cm bred förrötad granlåga</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1507,38 +1500,38 @@
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135484974</t>
+          <t>https://artportalen.se/Sighting/135484981</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>135484982</v>
+        <v>135484974</v>
       </c>
       <c r="B9" t="n">
-        <v>92497</v>
+        <v>92079</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1209</v>
+        <v>1204</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1548,10 +1541,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>644905</v>
+        <v>644999</v>
       </c>
       <c r="R9" t="n">
-        <v>6973584</v>
+        <v>6973387</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1597,7 +1590,7 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>gammal olikåldrig barrnaturskog i långsträckt bergssvacka</t>
+          <t>140-årig grannaturskog i blockig östsluttning</t>
         </is>
       </c>
       <c r="AN9" t="n">
@@ -1605,7 +1598,7 @@
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>1 substratenheter # 30 cm grov förrötad granlåga</t>
+          <t>1 substratenheter # gammal murken granlåga</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1626,7 +1619,1432 @@
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/135484974</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>136636547</v>
+      </c>
+      <c r="B10" t="n">
+        <v>92116</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>1204</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Gränsticka</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Phellopilus nigrolimitatus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Öst om spelåsen, Ång</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>644927</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6973463</v>
+      </c>
+      <c r="S10" t="n">
+        <v>3</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>16:52</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>16:52</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136636547</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>135484982</v>
+      </c>
+      <c r="B11" t="n">
+        <v>92497</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Hermanssonia centrifuga</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Spelåsens östsluttning, Ång</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>644905</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6973584</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>gammal olikåldrig barrnaturskog i långsträckt bergssvacka</t>
+        </is>
+      </c>
+      <c r="AN11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>1 substratenheter # 30 cm grov förrötad granlåga</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/135484982</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>136636546</v>
+      </c>
+      <c r="B12" t="n">
+        <v>92065</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Öst om spelåsen, Ång</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>644927</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6973465</v>
+      </c>
+      <c r="S12" t="n">
+        <v>3</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>16:51</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>16:51</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136636546</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>136636552</v>
+      </c>
+      <c r="B13" t="n">
+        <v>92065</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Öst om spelåsen, Ång</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>644780</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6973539</v>
+      </c>
+      <c r="S13" t="n">
+        <v>3</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>17:36</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>17:36</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136636552</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>136636556</v>
+      </c>
+      <c r="B14" t="n">
+        <v>92065</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Öst om spelåsen, Ång</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>644719</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6973635</v>
+      </c>
+      <c r="S14" t="n">
+        <v>3</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>18:04</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>18:04</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136636556</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>136636553</v>
+      </c>
+      <c r="B15" t="n">
+        <v>58003</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Öst om spelåsen, Ång</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>644756</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6973497</v>
+      </c>
+      <c r="S15" t="n">
+        <v>3</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>17:43</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>17:43</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136636553</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>136636549</v>
+      </c>
+      <c r="B16" t="n">
+        <v>58120</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>100090</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Nötkråka</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Nucifraga caryocatactes</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Öst om spelåsen, Ång</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>644820</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6973546</v>
+      </c>
+      <c r="S16" t="n">
+        <v>3</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>17:26</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>17:26</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136636549</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>136636554</v>
+      </c>
+      <c r="B17" t="n">
+        <v>58120</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>100090</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Nötkråka</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Nucifraga caryocatactes</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Öst om spelåsen, Ång</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>644762</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6973493</v>
+      </c>
+      <c r="S17" t="n">
+        <v>3</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>17:44</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>17:44</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136636554</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>136636548</v>
+      </c>
+      <c r="B18" t="n">
+        <v>58006</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Öst om spelåsen, Ång</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>644857</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6973531</v>
+      </c>
+      <c r="S18" t="n">
+        <v>3</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>17:16</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>17:16</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136636548</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>136636544</v>
+      </c>
+      <c r="B19" t="n">
+        <v>57998</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>100110</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Gråspett</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Picus canus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>J.F. Gmelin, 1788</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Öst om spelåsen, Ång</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>645003</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6973412</v>
+      </c>
+      <c r="S19" t="n">
+        <v>3</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>16:42</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>16:42</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136636544</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>136636550</v>
+      </c>
+      <c r="B20" t="n">
+        <v>99259</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Öst om spelåsen, Ång</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>644812</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6973547</v>
+      </c>
+      <c r="S20" t="n">
+        <v>3</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="inlineStr"/>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136636550</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>136636545</v>
+      </c>
+      <c r="B21" t="n">
+        <v>98204</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Öst om spelåsen, Ång</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>644928</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6973453</v>
+      </c>
+      <c r="S21" t="n">
+        <v>3</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>16:49</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>16:49</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136636545</t>
         </is>
       </c>
     </row>
@@ -1640,6 +3058,18 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 30534-2025 artfynd.xlsx
+++ b/artfynd/A 30534-2025 artfynd.xlsx
@@ -1159,7 +1159,7 @@
         <v>136636551</v>
       </c>
       <c r="B6" t="n">
-        <v>92373</v>
+        <v>92376</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1628,7 +1628,7 @@
         <v>136636547</v>
       </c>
       <c r="B10" t="n">
-        <v>92116</v>
+        <v>92119</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1859,7 +1859,7 @@
         <v>136636546</v>
       </c>
       <c r="B12" t="n">
-        <v>92065</v>
+        <v>92068</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1971,7 +1971,7 @@
         <v>136636552</v>
       </c>
       <c r="B13" t="n">
-        <v>92065</v>
+        <v>92068</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2083,7 +2083,7 @@
         <v>136636556</v>
       </c>
       <c r="B14" t="n">
-        <v>92065</v>
+        <v>92068</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2812,7 +2812,7 @@
         <v>136636550</v>
       </c>
       <c r="B20" t="n">
-        <v>99259</v>
+        <v>99262</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2941,7 +2941,7 @@
         <v>136636545</v>
       </c>
       <c r="B21" t="n">
-        <v>98204</v>
+        <v>98207</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 30534-2025 artfynd.xlsx
+++ b/artfynd/A 30534-2025 artfynd.xlsx
@@ -1159,7 +1159,7 @@
         <v>136636551</v>
       </c>
       <c r="B6" t="n">
-        <v>92376</v>
+        <v>92377</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1628,7 +1628,7 @@
         <v>136636547</v>
       </c>
       <c r="B10" t="n">
-        <v>92119</v>
+        <v>92120</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1859,7 +1859,7 @@
         <v>136636546</v>
       </c>
       <c r="B12" t="n">
-        <v>92068</v>
+        <v>92069</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1971,7 +1971,7 @@
         <v>136636552</v>
       </c>
       <c r="B13" t="n">
-        <v>92068</v>
+        <v>92069</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2083,7 +2083,7 @@
         <v>136636556</v>
       </c>
       <c r="B14" t="n">
-        <v>92068</v>
+        <v>92069</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2812,7 +2812,7 @@
         <v>136636550</v>
       </c>
       <c r="B20" t="n">
-        <v>99262</v>
+        <v>99263</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2941,7 +2941,7 @@
         <v>136636545</v>
       </c>
       <c r="B21" t="n">
-        <v>98207</v>
+        <v>98208</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 30534-2025 artfynd.xlsx
+++ b/artfynd/A 30534-2025 artfynd.xlsx
@@ -1159,7 +1159,7 @@
         <v>136636551</v>
       </c>
       <c r="B6" t="n">
-        <v>92377</v>
+        <v>92382</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1628,7 +1628,7 @@
         <v>136636547</v>
       </c>
       <c r="B10" t="n">
-        <v>92120</v>
+        <v>92125</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1859,7 +1859,7 @@
         <v>136636546</v>
       </c>
       <c r="B12" t="n">
-        <v>92069</v>
+        <v>92074</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1971,7 +1971,7 @@
         <v>136636552</v>
       </c>
       <c r="B13" t="n">
-        <v>92069</v>
+        <v>92074</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2083,7 +2083,7 @@
         <v>136636556</v>
       </c>
       <c r="B14" t="n">
-        <v>92069</v>
+        <v>92074</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2195,7 +2195,7 @@
         <v>136636553</v>
       </c>
       <c r="B15" t="n">
-        <v>58003</v>
+        <v>58005</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2315,7 +2315,7 @@
         <v>136636549</v>
       </c>
       <c r="B16" t="n">
-        <v>58120</v>
+        <v>58122</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2439,7 +2439,7 @@
         <v>136636554</v>
       </c>
       <c r="B17" t="n">
-        <v>58120</v>
+        <v>58122</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2567,7 +2567,7 @@
         <v>136636548</v>
       </c>
       <c r="B18" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2692,7 +2692,7 @@
         <v>136636544</v>
       </c>
       <c r="B19" t="n">
-        <v>57998</v>
+        <v>58000</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2812,7 +2812,7 @@
         <v>136636550</v>
       </c>
       <c r="B20" t="n">
-        <v>99263</v>
+        <v>99268</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2941,7 +2941,7 @@
         <v>136636545</v>
       </c>
       <c r="B21" t="n">
-        <v>98208</v>
+        <v>98213</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 30534-2025 artfynd.xlsx
+++ b/artfynd/A 30534-2025 artfynd.xlsx
@@ -1159,7 +1159,7 @@
         <v>136636551</v>
       </c>
       <c r="B6" t="n">
-        <v>92382</v>
+        <v>92384</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1628,7 +1628,7 @@
         <v>136636547</v>
       </c>
       <c r="B10" t="n">
-        <v>92125</v>
+        <v>92127</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1859,7 +1859,7 @@
         <v>136636546</v>
       </c>
       <c r="B12" t="n">
-        <v>92074</v>
+        <v>92076</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1971,7 +1971,7 @@
         <v>136636552</v>
       </c>
       <c r="B13" t="n">
-        <v>92074</v>
+        <v>92076</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2083,7 +2083,7 @@
         <v>136636556</v>
       </c>
       <c r="B14" t="n">
-        <v>92074</v>
+        <v>92076</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2812,7 +2812,7 @@
         <v>136636550</v>
       </c>
       <c r="B20" t="n">
-        <v>99268</v>
+        <v>99270</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2941,7 +2941,7 @@
         <v>136636545</v>
       </c>
       <c r="B21" t="n">
-        <v>98213</v>
+        <v>98215</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 30534-2025 artfynd.xlsx
+++ b/artfynd/A 30534-2025 artfynd.xlsx
@@ -1159,7 +1159,7 @@
         <v>136636551</v>
       </c>
       <c r="B6" t="n">
-        <v>92384</v>
+        <v>92386</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1628,7 +1628,7 @@
         <v>136636547</v>
       </c>
       <c r="B10" t="n">
-        <v>92127</v>
+        <v>92129</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1859,7 +1859,7 @@
         <v>136636546</v>
       </c>
       <c r="B12" t="n">
-        <v>92076</v>
+        <v>92078</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1971,7 +1971,7 @@
         <v>136636552</v>
       </c>
       <c r="B13" t="n">
-        <v>92076</v>
+        <v>92078</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2083,7 +2083,7 @@
         <v>136636556</v>
       </c>
       <c r="B14" t="n">
-        <v>92076</v>
+        <v>92078</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2812,7 +2812,7 @@
         <v>136636550</v>
       </c>
       <c r="B20" t="n">
-        <v>99270</v>
+        <v>99276</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2941,7 +2941,7 @@
         <v>136636545</v>
       </c>
       <c r="B21" t="n">
-        <v>98215</v>
+        <v>98221</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 30534-2025 artfynd.xlsx
+++ b/artfynd/A 30534-2025 artfynd.xlsx
@@ -1159,7 +1159,7 @@
         <v>136636551</v>
       </c>
       <c r="B6" t="n">
-        <v>92386</v>
+        <v>92388</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1628,7 +1628,7 @@
         <v>136636547</v>
       </c>
       <c r="B10" t="n">
-        <v>92129</v>
+        <v>92131</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1859,7 +1859,7 @@
         <v>136636546</v>
       </c>
       <c r="B12" t="n">
-        <v>92078</v>
+        <v>92080</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1971,7 +1971,7 @@
         <v>136636552</v>
       </c>
       <c r="B13" t="n">
-        <v>92078</v>
+        <v>92080</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2083,7 +2083,7 @@
         <v>136636556</v>
       </c>
       <c r="B14" t="n">
-        <v>92078</v>
+        <v>92080</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2812,7 +2812,7 @@
         <v>136636550</v>
       </c>
       <c r="B20" t="n">
-        <v>99276</v>
+        <v>99278</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2941,7 +2941,7 @@
         <v>136636545</v>
       </c>
       <c r="B21" t="n">
-        <v>98221</v>
+        <v>98223</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 30534-2025 artfynd.xlsx
+++ b/artfynd/A 30534-2025 artfynd.xlsx
@@ -1159,7 +1159,7 @@
         <v>136636551</v>
       </c>
       <c r="B6" t="n">
-        <v>92388</v>
+        <v>92389</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1628,7 +1628,7 @@
         <v>136636547</v>
       </c>
       <c r="B10" t="n">
-        <v>92131</v>
+        <v>92132</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1859,7 +1859,7 @@
         <v>136636546</v>
       </c>
       <c r="B12" t="n">
-        <v>92080</v>
+        <v>92081</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1971,7 +1971,7 @@
         <v>136636552</v>
       </c>
       <c r="B13" t="n">
-        <v>92080</v>
+        <v>92081</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2083,7 +2083,7 @@
         <v>136636556</v>
       </c>
       <c r="B14" t="n">
-        <v>92080</v>
+        <v>92081</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2812,7 +2812,7 @@
         <v>136636550</v>
       </c>
       <c r="B20" t="n">
-        <v>99278</v>
+        <v>99279</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2941,7 +2941,7 @@
         <v>136636545</v>
       </c>
       <c r="B21" t="n">
-        <v>98223</v>
+        <v>98224</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 30534-2025 artfynd.xlsx
+++ b/artfynd/A 30534-2025 artfynd.xlsx
@@ -1159,7 +1159,7 @@
         <v>136636551</v>
       </c>
       <c r="B6" t="n">
-        <v>92389</v>
+        <v>92395</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1628,7 +1628,7 @@
         <v>136636547</v>
       </c>
       <c r="B10" t="n">
-        <v>92132</v>
+        <v>92138</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1859,7 +1859,7 @@
         <v>136636546</v>
       </c>
       <c r="B12" t="n">
-        <v>92081</v>
+        <v>92087</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1971,7 +1971,7 @@
         <v>136636552</v>
       </c>
       <c r="B13" t="n">
-        <v>92081</v>
+        <v>92087</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2083,7 +2083,7 @@
         <v>136636556</v>
       </c>
       <c r="B14" t="n">
-        <v>92081</v>
+        <v>92087</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2812,7 +2812,7 @@
         <v>136636550</v>
       </c>
       <c r="B20" t="n">
-        <v>99279</v>
+        <v>99285</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2941,7 +2941,7 @@
         <v>136636545</v>
       </c>
       <c r="B21" t="n">
-        <v>98224</v>
+        <v>98230</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 30534-2025 artfynd.xlsx
+++ b/artfynd/A 30534-2025 artfynd.xlsx
@@ -1159,7 +1159,7 @@
         <v>136636551</v>
       </c>
       <c r="B6" t="n">
-        <v>92395</v>
+        <v>92399</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1628,7 +1628,7 @@
         <v>136636547</v>
       </c>
       <c r="B10" t="n">
-        <v>92138</v>
+        <v>92142</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1859,7 +1859,7 @@
         <v>136636546</v>
       </c>
       <c r="B12" t="n">
-        <v>92087</v>
+        <v>92091</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1971,7 +1971,7 @@
         <v>136636552</v>
       </c>
       <c r="B13" t="n">
-        <v>92087</v>
+        <v>92091</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2083,7 +2083,7 @@
         <v>136636556</v>
       </c>
       <c r="B14" t="n">
-        <v>92087</v>
+        <v>92091</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2812,7 +2812,7 @@
         <v>136636550</v>
       </c>
       <c r="B20" t="n">
-        <v>99285</v>
+        <v>99289</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2941,7 +2941,7 @@
         <v>136636545</v>
       </c>
       <c r="B21" t="n">
-        <v>98230</v>
+        <v>98234</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 30534-2025 artfynd.xlsx
+++ b/artfynd/A 30534-2025 artfynd.xlsx
@@ -2812,7 +2812,7 @@
         <v>136636550</v>
       </c>
       <c r="B20" t="n">
-        <v>99289</v>
+        <v>99291</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2941,7 +2941,7 @@
         <v>136636545</v>
       </c>
       <c r="B21" t="n">
-        <v>98234</v>
+        <v>98236</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 30534-2025 artfynd.xlsx
+++ b/artfynd/A 30534-2025 artfynd.xlsx
@@ -1159,7 +1159,7 @@
         <v>136636551</v>
       </c>
       <c r="B6" t="n">
-        <v>92399</v>
+        <v>92401</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1628,7 +1628,7 @@
         <v>136636547</v>
       </c>
       <c r="B10" t="n">
-        <v>92142</v>
+        <v>92144</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1859,7 +1859,7 @@
         <v>136636546</v>
       </c>
       <c r="B12" t="n">
-        <v>92091</v>
+        <v>92093</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1971,7 +1971,7 @@
         <v>136636552</v>
       </c>
       <c r="B13" t="n">
-        <v>92091</v>
+        <v>92093</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2083,7 +2083,7 @@
         <v>136636556</v>
       </c>
       <c r="B14" t="n">
-        <v>92091</v>
+        <v>92093</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2812,7 +2812,7 @@
         <v>136636550</v>
       </c>
       <c r="B20" t="n">
-        <v>99291</v>
+        <v>99293</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2941,7 +2941,7 @@
         <v>136636545</v>
       </c>
       <c r="B21" t="n">
-        <v>98236</v>
+        <v>98238</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 30534-2025 artfynd.xlsx
+++ b/artfynd/A 30534-2025 artfynd.xlsx
@@ -1159,7 +1159,7 @@
         <v>136636551</v>
       </c>
       <c r="B6" t="n">
-        <v>92401</v>
+        <v>92414</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1628,7 +1628,7 @@
         <v>136636547</v>
       </c>
       <c r="B10" t="n">
-        <v>92144</v>
+        <v>92157</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1859,7 +1859,7 @@
         <v>136636546</v>
       </c>
       <c r="B12" t="n">
-        <v>92093</v>
+        <v>92106</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1971,7 +1971,7 @@
         <v>136636552</v>
       </c>
       <c r="B13" t="n">
-        <v>92093</v>
+        <v>92106</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2083,7 +2083,7 @@
         <v>136636556</v>
       </c>
       <c r="B14" t="n">
-        <v>92093</v>
+        <v>92106</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2195,7 +2195,7 @@
         <v>136636553</v>
       </c>
       <c r="B15" t="n">
-        <v>58005</v>
+        <v>58018</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2315,7 +2315,7 @@
         <v>136636549</v>
       </c>
       <c r="B16" t="n">
-        <v>58122</v>
+        <v>58135</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2439,7 +2439,7 @@
         <v>136636554</v>
       </c>
       <c r="B17" t="n">
-        <v>58122</v>
+        <v>58135</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2567,7 +2567,7 @@
         <v>136636548</v>
       </c>
       <c r="B18" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2692,7 +2692,7 @@
         <v>136636544</v>
       </c>
       <c r="B19" t="n">
-        <v>58000</v>
+        <v>58013</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2812,7 +2812,7 @@
         <v>136636550</v>
       </c>
       <c r="B20" t="n">
-        <v>99293</v>
+        <v>99306</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2941,7 +2941,7 @@
         <v>136636545</v>
       </c>
       <c r="B21" t="n">
-        <v>98238</v>
+        <v>98251</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 30534-2025 artfynd.xlsx
+++ b/artfynd/A 30534-2025 artfynd.xlsx
@@ -1159,7 +1159,7 @@
         <v>136636551</v>
       </c>
       <c r="B6" t="n">
-        <v>92414</v>
+        <v>92416</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1628,7 +1628,7 @@
         <v>136636547</v>
       </c>
       <c r="B10" t="n">
-        <v>92157</v>
+        <v>92159</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1859,7 +1859,7 @@
         <v>136636546</v>
       </c>
       <c r="B12" t="n">
-        <v>92106</v>
+        <v>92108</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1971,7 +1971,7 @@
         <v>136636552</v>
       </c>
       <c r="B13" t="n">
-        <v>92106</v>
+        <v>92108</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2083,7 +2083,7 @@
         <v>136636556</v>
       </c>
       <c r="B14" t="n">
-        <v>92106</v>
+        <v>92108</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2195,7 +2195,7 @@
         <v>136636553</v>
       </c>
       <c r="B15" t="n">
-        <v>58018</v>
+        <v>58020</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2315,7 +2315,7 @@
         <v>136636549</v>
       </c>
       <c r="B16" t="n">
-        <v>58135</v>
+        <v>58137</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2439,7 +2439,7 @@
         <v>136636554</v>
       </c>
       <c r="B17" t="n">
-        <v>58135</v>
+        <v>58137</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2567,7 +2567,7 @@
         <v>136636548</v>
       </c>
       <c r="B18" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2692,7 +2692,7 @@
         <v>136636544</v>
       </c>
       <c r="B19" t="n">
-        <v>58013</v>
+        <v>58015</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2812,7 +2812,7 @@
         <v>136636550</v>
       </c>
       <c r="B20" t="n">
-        <v>99306</v>
+        <v>99308</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2941,7 +2941,7 @@
         <v>136636545</v>
       </c>
       <c r="B21" t="n">
-        <v>98251</v>
+        <v>98253</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
